--- a/data/export/2026-10-10-operations.xlsx
+++ b/data/export/2026-10-10-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -991,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1068,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1211,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1222,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1467,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1483,12 +1515,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1534,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1570,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1918,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1979,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2375,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2451,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2470,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2495,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,25 +2506,25 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2494,49 +2534,45 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2560,17 +2596,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2580,45 +2616,41 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2651,12 +2683,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2670,7 +2702,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2706,35 +2738,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2767,12 +2799,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2818,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2854,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2883,12 +2915,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2934,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,35 +2970,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2999,12 +3031,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3018,7 +3050,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3054,7 +3086,3719 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-operations.xlsx
+++ b/data/export/2026-10-10-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -450,7 +450,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>71.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:33</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1139,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,17 +1200,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1216,13 +1220,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1559,7 +1583,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1570,7 +1594,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1627,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -1636,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1688,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1751,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1752,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1812,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1958,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2078,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2194,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2260,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2310,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2376,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2385,12 +2425,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2443,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2456,7 +2496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2470,7 +2510,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2500,41 +2540,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2567,12 +2611,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2586,7 +2630,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2611,46 +2655,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2683,12 +2731,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2702,7 +2750,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2727,46 +2775,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2799,12 +2851,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2818,7 +2870,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2854,35 +2906,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2915,12 +2967,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2934,7 +2986,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2959,46 +3011,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3031,12 +3087,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3050,7 +3106,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3075,46 +3131,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3147,12 +3207,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3166,7 +3226,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3191,7 +3251,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3202,35 +3262,35 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3263,12 +3323,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3282,7 +3342,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3307,46 +3367,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3379,12 +3443,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3398,7 +3462,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3423,18 +3487,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3447,60 +3515,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3514,7 +3586,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3524,33 +3596,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3563,60 +3639,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3630,7 +3710,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3640,33 +3720,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3679,60 +3763,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3746,7 +3834,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3756,17 +3844,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3776,13 +3864,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3887,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3805,7 +3897,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3843,12 +3935,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3862,7 +3954,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3898,7 +3990,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3911,7 +4003,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3921,7 +4013,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3931,12 +4023,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3959,12 +4051,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3972,13 +4064,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4014,7 +4122,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4027,22 +4135,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,12 +4183,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4094,7 +4202,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4130,7 +4238,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4251,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4153,7 +4261,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4191,12 +4299,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4210,7 +4318,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4246,7 +4354,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4367,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4269,7 +4377,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4307,12 +4415,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4326,7 +4434,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4362,7 +4470,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4483,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4385,7 +4493,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4423,12 +4531,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4442,7 +4550,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4478,7 +4586,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4491,22 +4599,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4539,12 +4647,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4558,7 +4666,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4594,7 +4702,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4607,22 +4715,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4655,12 +4763,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4782,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4710,7 +4818,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4723,22 +4831,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4771,12 +4879,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4898,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4826,35 +4934,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4887,12 +4995,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +5014,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4931,7 +5039,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4942,35 +5050,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5003,12 +5111,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5022,7 +5130,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5058,35 +5166,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5119,12 +5227,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5138,7 +5246,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5174,35 +5282,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5235,12 +5343,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5254,7 +5362,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5290,35 +5398,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5351,12 +5459,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5370,7 +5478,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5406,35 +5514,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5467,12 +5575,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5486,7 +5594,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5522,35 +5630,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5583,12 +5691,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5602,7 +5710,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5638,35 +5746,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5699,12 +5807,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5718,7 +5826,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5754,35 +5862,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5815,12 +5923,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5834,7 +5942,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5870,35 +5978,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5931,12 +6039,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5950,7 +6058,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5986,35 +6094,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6047,12 +6155,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6066,7 +6174,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6102,35 +6210,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6163,12 +6271,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6182,7 +6290,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6218,35 +6326,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6279,12 +6387,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6298,7 +6406,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6334,35 +6442,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6395,12 +6503,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6414,7 +6522,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6450,35 +6558,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6511,12 +6619,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6530,7 +6638,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6566,35 +6674,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6627,12 +6735,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6646,7 +6754,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6682,35 +6790,35 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6743,12 +6851,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6762,43 +6870,3103 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
           <t>08:05</t>
         </is>
       </c>
-      <c r="W54" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X54" s="2" t="inlineStr">
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y54" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z54" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
+      <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC54" s="2" t="inlineStr"/>
-      <c r="AD54" s="2" t="inlineStr">
-        <is>
-          <t>—/16</t>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-operations.xlsx
+++ b/data/export/2026-10-10-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -447,7 +447,7 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="36" customWidth="1" min="21" max="21"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1397,19 +1397,19 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1637,24 +1637,24 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1761,24 +1761,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1875,32 +1875,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1908,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1932,33 +1936,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1991,32 +1999,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2024,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2048,37 +2060,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2111,32 +2123,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2144,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2168,33 +2184,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2227,32 +2247,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2260,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2284,33 +2308,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2404,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2415,7 +2443,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2430,7 +2458,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2463,32 +2491,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2496,7 +2528,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2520,17 +2552,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2540,17 +2572,17 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2648,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2670,7 +2702,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2768,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2775,7 +2807,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2790,7 +2822,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2972,7 +3004,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3026,7 +3058,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3124,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3141,12 +3173,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3244,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3328,7 +3360,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3377,12 +3409,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3480,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3497,82 +3529,78 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3586,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3596,17 +3624,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3621,82 +3649,78 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3710,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3720,107 +3744,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3834,7 +3854,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3844,65 +3864,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3935,12 +3955,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3954,7 +3974,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3979,56 +3999,60 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4051,12 +4075,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4064,29 +4088,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>丁香路锦绣路</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:36</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:43</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4111,46 +4119,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4183,12 +4195,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4202,7 +4214,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4227,18 +4239,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4251,52 +4267,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4304,7 +4324,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4318,7 +4338,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4328,33 +4348,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4367,60 +4391,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4434,7 +4462,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4444,33 +4472,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4483,60 +4515,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4550,7 +4586,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4560,33 +4596,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4599,60 +4639,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4666,7 +4710,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4676,33 +4720,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4715,32 +4763,32 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4763,12 +4811,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4776,13 +4824,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4807,7 +4871,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4831,60 +4895,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4898,7 +4966,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4908,33 +4976,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4947,60 +5019,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5014,7 +5090,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5024,33 +5100,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5063,60 +5143,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5130,7 +5214,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5140,33 +5224,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5267,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5189,7 +5277,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5199,40 +5287,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5246,7 +5338,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5256,33 +5348,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5391,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5305,7 +5401,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5315,40 +5411,44 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5362,7 +5462,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5372,33 +5472,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5515,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5421,7 +5525,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5459,12 +5563,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5478,7 +5582,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5527,7 +5631,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5537,7 +5641,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5547,12 +5651,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5575,12 +5679,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5588,13 +5692,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5643,7 +5763,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5653,7 +5773,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5691,12 +5811,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5710,7 +5830,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5759,22 +5879,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5807,12 +5927,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5826,7 +5946,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5875,7 +5995,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5885,7 +6005,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5895,12 +6015,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq45推进至seq47，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5923,12 +6043,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5936,13 +6056,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq19（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5991,22 +6123,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6039,12 +6171,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6058,7 +6190,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6107,22 +6239,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6155,12 +6287,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6174,7 +6306,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6223,7 +6355,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6233,7 +6365,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6271,12 +6403,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6290,7 +6422,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6339,7 +6471,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6349,7 +6481,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6387,12 +6519,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6406,7 +6538,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6455,22 +6587,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6503,12 +6635,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6522,7 +6654,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6571,22 +6703,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6619,12 +6751,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6638,7 +6770,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6687,7 +6819,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6697,7 +6829,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6735,12 +6867,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6754,7 +6886,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6803,7 +6935,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6813,7 +6945,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6851,12 +6983,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6870,7 +7002,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6895,22 +7027,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6923,7 +7051,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6933,7 +7061,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6971,12 +7099,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6990,7 +7118,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7015,92 +7143,84 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>126.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7114,7 +7234,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7124,107 +7244,99 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7238,7 +7350,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7248,107 +7360,99 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7362,7 +7466,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7372,65 +7476,61 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7463,12 +7563,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7482,7 +7582,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7518,35 +7618,35 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7579,12 +7679,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7598,7 +7698,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7628,41 +7728,45 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7695,12 +7799,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7714,7 +7818,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7744,41 +7848,45 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7811,12 +7919,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7830,7 +7938,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7855,46 +7963,50 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7927,12 +8039,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7946,7 +8058,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7976,41 +8088,45 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8043,12 +8159,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8062,7 +8178,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8087,7 +8203,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8098,35 +8214,35 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8159,12 +8275,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8178,7 +8294,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8208,41 +8324,45 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8275,12 +8395,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8294,7 +8414,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8319,46 +8439,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8391,12 +8515,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8410,7 +8534,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8435,46 +8559,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8507,12 +8635,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8526,7 +8654,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8551,46 +8679,50 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8623,12 +8755,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8642,7 +8774,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8667,18 +8799,22 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8691,52 +8827,56 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8744,7 +8884,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8758,7 +8898,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8768,33 +8908,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8951,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8817,7 +8961,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8827,40 +8971,44 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8874,7 +9022,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8884,33 +9032,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8923,7 +9075,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8933,7 +9085,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8943,40 +9095,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8990,7 +9146,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9000,17 +9156,17 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9025,12 +9181,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9199,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9053,7 +9209,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9063,40 +9219,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9110,7 +9270,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9120,33 +9280,37 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9159,22 +9323,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9212,7 +9376,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9226,7 +9390,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9256,17 +9420,13 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9279,22 +9439,22 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9327,12 +9487,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9346,7 +9506,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9371,22 +9531,18 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9555,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9409,7 +9565,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9419,40 +9575,44 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9466,7 +9626,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9476,17 +9636,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9496,13 +9656,17 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9679,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9525,7 +9689,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9535,40 +9699,44 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9582,7 +9750,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9592,17 +9760,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9612,13 +9780,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9631,22 +9803,22 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9679,12 +9851,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9698,7 +9870,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9723,7 +9895,7 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
@@ -9747,60 +9919,64 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9814,7 +9990,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9824,17 +10000,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9844,13 +10020,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9863,7 +10043,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9873,7 +10053,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9883,40 +10063,44 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9930,41 +10114,2921 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="W80" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X80" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y80" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z80" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC80" s="2" t="inlineStr"/>
-      <c r="AD80" s="2" t="inlineStr">
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-10-operations.xlsx
+++ b/data/export/2026-10-10-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD104"/>
+  <dimension ref="A1:AD113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2567,14 +2567,14 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2735,32 +2735,36 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2768,7 +2772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2792,17 +2796,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2812,7 +2816,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2822,7 +2826,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2855,32 +2859,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -2888,7 +2896,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2912,17 +2920,17 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2932,13 +2940,17 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2971,32 +2983,36 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -3004,7 +3020,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3028,37 +3044,37 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3178,7 +3194,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3260,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3360,7 +3376,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3414,7 +3430,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3496,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3534,7 +3550,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3616,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3654,7 +3670,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3736,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3774,7 +3790,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3856,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3894,7 +3910,7 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3976,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4014,7 +4030,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4096,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4147,22 +4163,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4200,7 +4216,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4214,7 +4230,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4244,87 +4260,83 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4338,7 +4350,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4348,107 +4360,103 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4462,7 +4470,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4472,22 +4480,22 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4497,82 +4505,78 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4586,7 +4590,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4596,37 +4600,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4639,24 +4643,24 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4669,24 +4673,24 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4696,7 +4700,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4710,7 +4714,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4745,12 +4749,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4763,52 +4767,56 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>06:36</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4816,7 +4824,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4824,29 +4832,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>丁香路锦绣路</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>07:36</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>07:43</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4856,17 +4848,17 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4876,13 +4868,17 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4891,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4905,7 +4901,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4925,34 +4921,34 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4966,7 +4962,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5001,12 +4997,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5015,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5029,7 +5025,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5049,24 +5045,24 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5076,7 +5072,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5090,7 +5086,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5125,12 +5121,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5139,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5153,7 +5149,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5163,44 +5159,40 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5208,13 +5200,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr"/>
-      <c r="T39" s="2" t="inlineStr"/>
-      <c r="U39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5224,17 +5232,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5244,17 +5252,13 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5267,24 +5271,24 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5297,34 +5301,34 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5338,7 +5342,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5373,12 +5377,12 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5391,24 +5395,24 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5421,12 +5425,12 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
@@ -5443,12 +5447,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5462,7 +5466,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5497,12 +5501,12 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5515,60 +5519,64 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5582,7 +5590,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5592,33 +5600,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5643,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5641,7 +5653,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5651,40 +5663,44 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5692,29 +5708,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>物理seq24（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>08:24</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>08:32</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5724,33 +5724,37 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5767,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5773,7 +5777,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5783,40 +5787,44 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5830,7 +5838,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5840,33 +5848,37 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5891,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5889,7 +5901,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5899,40 +5911,44 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5946,7 +5962,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5956,33 +5972,37 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5995,7 +6015,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -6005,7 +6025,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6020,7 +6040,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq45推进至seq47，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq63，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -6043,12 +6063,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6058,23 +6078,27 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>物理seq19（站名待映射）</t>
+          <t>物理seq24（站名待映射）</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr"/>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6123,7 +6147,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6133,7 +6157,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6143,40 +6167,44 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6190,7 +6218,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6200,33 +6228,37 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6271,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6249,7 +6281,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6287,12 +6319,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6306,7 +6338,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6331,7 +6363,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6355,7 +6387,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6365,7 +6397,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6375,12 +6407,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq45推进至seq58，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -6403,12 +6435,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6416,13 +6448,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R49" s="2" t="inlineStr"/>
-      <c r="S49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>物理seq19（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
       <c r="T49" s="2" t="inlineStr"/>
-      <c r="U49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6471,7 +6515,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6481,7 +6525,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6519,12 +6563,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6538,7 +6582,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6587,22 +6631,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6640,7 +6684,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6654,7 +6698,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6703,7 +6747,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6713,7 +6757,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6751,12 +6795,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6770,7 +6814,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6819,22 +6863,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6867,12 +6911,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6886,7 +6930,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6935,7 +6979,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6945,7 +6989,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6983,12 +7027,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7002,7 +7046,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -7051,7 +7095,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -7061,7 +7105,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -7099,12 +7143,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7118,7 +7162,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7167,22 +7211,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7220,7 +7264,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7234,7 +7278,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7283,22 +7327,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7331,12 +7375,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7350,7 +7394,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7399,22 +7443,22 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7447,12 +7491,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7466,7 +7510,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7515,22 +7559,22 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7563,12 +7607,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7582,7 +7626,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7631,22 +7675,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7684,7 +7728,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7698,7 +7742,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7723,22 +7767,18 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7751,22 +7791,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7804,7 +7844,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7818,7 +7858,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7843,22 +7883,18 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>126.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7907,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7881,7 +7917,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7919,12 +7955,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7938,7 +7974,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7963,22 +7999,18 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7991,7 +8023,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -8001,7 +8033,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -8044,7 +8076,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8058,7 +8090,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8093,12 +8125,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -8111,22 +8143,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8164,7 +8196,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8178,7 +8210,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8208,13 +8240,17 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8263,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8237,7 +8273,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8275,12 +8311,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8294,7 +8330,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8329,12 +8365,12 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8383,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8357,7 +8393,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8400,7 +8436,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8414,7 +8450,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8449,12 +8485,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -8467,22 +8503,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8515,12 +8551,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8534,7 +8570,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8564,17 +8600,13 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8587,22 +8619,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8635,12 +8667,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8654,7 +8686,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8689,12 +8721,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -8707,22 +8739,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8755,12 +8787,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8774,7 +8806,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8809,82 +8841,78 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8898,7 +8926,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8908,17 +8936,17 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8928,87 +8956,83 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9022,7 +9046,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9032,22 +9056,22 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -9057,82 +9081,78 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9146,7 +9166,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9156,17 +9176,17 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9181,82 +9201,78 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9270,7 +9286,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9280,17 +9296,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9305,40 +9321,40 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9371,12 +9387,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9390,7 +9406,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9426,35 +9442,35 @@
       <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9487,12 +9503,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9506,7 +9522,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9531,18 +9547,22 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9575,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9565,7 +9585,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9585,12 +9605,12 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
@@ -9607,12 +9627,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9626,7 +9646,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9656,17 +9676,17 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9679,24 +9699,24 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9709,34 +9729,34 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9750,7 +9770,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9775,7 +9795,7 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -9785,12 +9805,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9803,60 +9823,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9870,7 +9894,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9880,33 +9904,37 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB78" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9919,24 +9947,24 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9949,12 +9977,12 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
@@ -9971,12 +9999,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9990,7 +10018,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -10025,12 +10053,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10043,64 +10071,60 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10114,7 +10138,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10124,37 +10148,33 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10167,7 +10187,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -10177,7 +10197,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10187,44 +10207,40 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10238,7 +10254,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10248,37 +10264,33 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC81" s="2" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10291,24 +10303,24 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10321,34 +10333,34 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10362,7 +10374,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10387,7 +10399,7 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
@@ -10397,12 +10409,12 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10415,24 +10427,24 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10445,34 +10457,34 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10486,7 +10498,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10511,22 +10523,22 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB83" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10539,64 +10551,60 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10610,7 +10618,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10620,17 +10628,17 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10640,17 +10648,13 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC84" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10663,24 +10667,24 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10693,12 +10697,12 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
@@ -10715,12 +10719,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10734,7 +10738,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10759,22 +10763,22 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB85" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10787,24 +10791,24 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>08:05</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10817,34 +10821,34 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10858,7 +10862,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10888,17 +10892,17 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10915,7 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -10921,7 +10925,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10931,40 +10935,44 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10978,7 +10986,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10988,17 +10996,17 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -11008,13 +11016,17 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC87" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11027,60 +11039,64 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11094,7 +11110,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -11104,17 +11120,17 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
@@ -11129,12 +11145,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11147,60 +11163,64 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11214,7 +11234,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11224,22 +11244,22 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
@@ -11249,12 +11269,12 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11267,60 +11287,64 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11334,7 +11358,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11344,17 +11368,17 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11364,13 +11388,17 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC90" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11383,55 +11411,59 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11450,7 +11482,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11460,33 +11492,37 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11499,7 +11535,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11509,7 +11545,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11519,40 +11555,44 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11566,7 +11606,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11576,33 +11616,37 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC92" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11615,60 +11659,64 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11682,7 +11730,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11692,17 +11740,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11717,12 +11765,12 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11783,7 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -11745,7 +11793,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11755,32 +11803,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11788,7 +11840,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11802,7 +11854,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11812,37 +11864,37 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11907,7 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -11865,7 +11917,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -11903,12 +11955,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11922,7 +11974,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11947,7 +11999,7 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
@@ -11957,12 +12009,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11975,7 +12027,7 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -11985,7 +12037,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -12023,12 +12075,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12042,7 +12094,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -12067,22 +12119,18 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC96" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr"/>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12143,7 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -12105,7 +12153,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -12143,12 +12191,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12162,7 +12210,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -12187,7 +12235,7 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
@@ -12211,7 +12259,7 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -12221,7 +12269,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -12259,12 +12307,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12278,7 +12326,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -12303,22 +12351,18 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12331,22 +12375,22 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -12379,12 +12423,12 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12398,7 +12442,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -12433,12 +12477,12 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12451,22 +12495,22 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -12499,12 +12543,12 @@
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12518,7 +12562,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12553,12 +12597,12 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -12571,22 +12615,22 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -12619,12 +12663,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12638,7 +12682,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12663,7 +12707,7 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
@@ -12691,22 +12735,22 @@
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -12739,12 +12783,12 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -12758,7 +12802,7 @@
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12788,13 +12832,17 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC102" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12807,22 +12855,22 @@
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -12855,12 +12903,12 @@
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12874,7 +12922,7 @@
       <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
@@ -12899,22 +12947,18 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC103" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12927,22 +12971,22 @@
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12975,12 +13019,12 @@
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12994,43 +13038,1119 @@
       <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" s="2" t="inlineStr">
         <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD104" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD105" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD106" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr"/>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD107" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD108" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD109" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr"/>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AD110" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="W104" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr"/>
+      <c r="S111" s="2" t="inlineStr"/>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X104" s="2" t="inlineStr">
+      <c r="X111" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y104" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z104" s="2" t="inlineStr">
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z111" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA104" s="2" t="inlineStr">
+      <c r="AA111" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB104" s="2" t="inlineStr">
+      <c r="AB111" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC104" s="2" t="inlineStr"/>
-      <c r="AD104" s="2" t="inlineStr">
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr"/>
+      <c r="S112" s="2" t="inlineStr"/>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z112" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA112" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB112" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr"/>
+      <c r="S113" s="2" t="inlineStr"/>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z113" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA113" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC113" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD113" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-operations.xlsx
+++ b/data/export/2026-10-10-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3812,17 +3812,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3936,17 +3936,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5300,17 +5300,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5424,17 +5424,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10248,17 +10248,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10744,17 +10744,17 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11657,24 +11657,24 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
@@ -11771,32 +11771,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11804,7 +11808,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11828,17 +11832,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11848,17 +11852,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11891,32 +11895,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11924,7 +11932,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11948,17 +11956,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11968,17 +11976,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -12011,32 +12019,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12044,7 +12056,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12068,17 +12080,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12088,7 +12100,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -12164,7 +12176,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12284,7 +12296,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12333,7 +12345,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12404,7 +12416,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12448,17 +12460,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12540,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12572,17 +12584,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12718,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12842,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12966,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13168,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13210,7 +13222,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13280,7 +13292,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13458,7 +13470,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13594,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13664,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13830,7 +13842,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13978,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14102,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14172,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14204,17 +14216,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14292,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14346,7 +14358,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14428,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14470,7 +14482,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14548,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14580,12 +14592,12 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
@@ -14656,7 +14668,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14700,17 +14712,17 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14842,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -14900,7 +14912,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14944,17 +14956,17 @@
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15036,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15078,7 +15090,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15214,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -15326,7 +15338,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -15446,7 +15458,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -15636,7 +15648,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15680,17 +15692,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -15814,7 +15826,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -16054,7 +16066,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -16120,7 +16132,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16164,17 +16176,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -16294,7 +16306,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -16418,7 +16430,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16632,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16674,7 +16686,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -16744,7 +16756,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16922,7 +16934,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -17046,7 +17058,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17128,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17294,7 +17306,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17364,7 +17376,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17408,17 +17420,17 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -17542,7 +17554,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -17612,7 +17624,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17656,12 +17668,12 @@
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
@@ -17736,7 +17748,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17790,7 +17802,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -17860,7 +17872,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17904,17 +17916,17 @@
       </c>
       <c r="AB141" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -18038,7 +18050,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18120,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18152,17 +18164,17 @@
       </c>
       <c r="AB143" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -18232,7 +18244,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18286,7 +18298,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -18410,7 +18422,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -18534,7 +18546,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18670,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18794,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18918,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -19030,7 +19042,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -19154,7 +19166,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -19278,7 +19290,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -19534,7 +19546,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -19658,7 +19670,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -19728,7 +19740,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19782,7 +19794,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -19906,7 +19918,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -19976,7 +19988,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20020,12 +20032,12 @@
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
@@ -20154,7 +20166,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -20224,7 +20236,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20278,7 +20290,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20414,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -20526,7 +20538,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20662,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20786,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -20898,7 +20910,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -20968,7 +20980,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21146,7 +21158,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21356,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21388,17 +21400,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21480,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21512,17 +21524,17 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21600,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21704,7 +21716,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21748,17 +21760,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -21828,7 +21840,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21882,7 +21894,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -21952,7 +21964,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21996,17 +22008,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22142,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -22200,7 +22212,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22254,7 +22266,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -22378,7 +22390,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -22448,7 +22460,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22626,7 +22638,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -22750,7 +22762,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22886,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22944,7 +22956,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22998,7 +23010,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -23122,7 +23134,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -23246,7 +23258,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23370,7 +23382,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -23425,12 +23437,12 @@
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O186" s="2" t="inlineStr">
@@ -23440,7 +23452,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23614,7 +23626,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -23738,7 +23750,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -23771,32 +23783,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23804,7 +23820,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23828,17 +23844,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23848,17 +23864,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -23891,32 +23907,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23924,7 +23944,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23948,17 +23968,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23968,17 +23988,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -24011,32 +24031,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -24044,7 +24068,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24068,17 +24092,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24088,12 +24112,12 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
@@ -24218,7 +24242,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -24251,32 +24275,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24284,7 +24312,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24308,17 +24336,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24328,17 +24356,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -24371,32 +24399,36 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -24404,7 +24436,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24428,17 +24460,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24448,17 +24480,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -24524,7 +24556,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24578,7 +24610,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -24611,32 +24643,36 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -24644,7 +24680,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24668,17 +24704,17 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
@@ -24688,17 +24724,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -24764,7 +24800,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24818,7 +24854,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24920,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24938,7 +24974,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -25004,7 +25040,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25124,7 +25160,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25178,7 +25214,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -25244,7 +25280,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25288,17 +25324,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -25368,7 +25404,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25412,17 +25448,17 @@
       </c>
       <c r="AB202" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -25740,7 +25776,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25794,7 +25830,7 @@
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -25860,7 +25896,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25909,12 +25945,12 @@
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -26034,7 +26070,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -26158,7 +26194,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26384,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26397,7 +26433,7 @@
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
@@ -26472,7 +26508,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26516,17 +26552,17 @@
       </c>
       <c r="AB211" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -26650,7 +26686,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -27022,7 +27058,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -27270,7 +27306,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -27340,7 +27376,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27384,17 +27420,17 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -27464,7 +27500,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27508,17 +27544,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -27828,7 +27864,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27877,12 +27913,12 @@
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -28002,7 +28038,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28184,7 +28220,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28238,7 +28274,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28518,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28552,7 +28588,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28596,17 +28632,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28712,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28725,7 +28761,7 @@
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
@@ -28854,7 +28890,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -29292,7 +29328,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29336,17 +29372,17 @@
       </c>
       <c r="AB234" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC234" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -29718,7 +29754,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -29784,7 +29820,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29845,12 +29881,12 @@
       </c>
       <c r="AC238" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -30098,7 +30134,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -30164,7 +30200,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30220,17 +30256,17 @@
       </c>
       <c r="AB241" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30478,7 +30514,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -31098,7 +31134,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31346,7 +31382,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -31594,7 +31630,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -32214,7 +32250,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32284,7 +32320,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32328,17 +32364,17 @@
       </c>
       <c r="AB258" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC258" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -32582,7 +32618,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -32830,7 +32866,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -32900,7 +32936,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32954,7 +32990,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -33078,7 +33114,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -33268,7 +33304,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33317,7 +33353,7 @@
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
@@ -33442,7 +33478,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -33636,7 +33672,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33685,12 +33721,12 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -33760,7 +33796,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33804,17 +33840,17 @@
       </c>
       <c r="AB270" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -34008,7 +34044,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34052,17 +34088,17 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -34310,7 +34346,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34504,7 +34540,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34548,17 +34584,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -34682,7 +34718,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -34930,7 +34966,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -35054,7 +35090,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -35124,7 +35160,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35178,7 +35214,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35368,7 +35404,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35417,7 +35453,7 @@
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
@@ -35546,7 +35582,7 @@
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35740,7 +35776,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35789,12 +35825,12 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -35864,7 +35900,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35908,17 +35944,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36268,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36276,17 +36312,17 @@
       </c>
       <c r="AB290" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36534,7 +36570,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36724,7 +36760,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36768,17 +36804,17 @@
       </c>
       <c r="AB294" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -36902,7 +36938,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -37026,7 +37062,7 @@
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -37150,7 +37186,7 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37220,7 +37256,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37274,7 +37310,7 @@
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -37317,12 +37353,12 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
@@ -37344,7 +37380,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37393,12 +37429,12 @@
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -37441,24 +37477,24 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr"/>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N300" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O300" s="2" t="inlineStr">
@@ -37468,7 +37504,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37517,7 +37553,7 @@
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
@@ -37555,32 +37591,36 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N301" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O301" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37588,7 +37628,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37612,17 +37652,17 @@
       </c>
       <c r="X301" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z301" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA301" s="2" t="inlineStr">
@@ -37632,17 +37672,17 @@
       </c>
       <c r="AB301" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37675,32 +37715,36 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N302" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O302" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -37708,7 +37752,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37732,17 +37776,17 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA302" s="2" t="inlineStr">
@@ -37752,17 +37796,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -37795,32 +37839,36 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -37828,7 +37876,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37852,17 +37900,17 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA303" s="2" t="inlineStr">
@@ -37872,17 +37920,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -37948,7 +37996,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38002,7 +38050,7 @@
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -38068,7 +38116,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38117,7 +38165,7 @@
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
@@ -38188,7 +38236,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38232,17 +38280,17 @@
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-operations.xlsx
+++ b/data/export/2026-10-10-operations.xlsx
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6168,17 +6168,17 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8520,17 +8520,17 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9636,12 +9636,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10000,17 +10000,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10248,12 +10248,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11356,12 +11356,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11728,17 +11728,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11976,12 +11976,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -12143,32 +12143,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12176,7 +12180,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12200,17 +12204,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12220,12 +12224,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12263,32 +12267,36 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -12296,7 +12304,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12320,17 +12328,17 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -12340,17 +12348,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12383,32 +12391,36 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:24</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -12416,7 +12428,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12440,17 +12452,17 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
@@ -12460,12 +12472,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -13168,7 +13180,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13212,17 +13224,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13676,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13708,17 +13720,17 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13842,7 +13854,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14114,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -14226,7 +14238,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -14428,7 +14440,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14482,7 +14494,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -14668,7 +14680,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14912,7 +14924,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15036,7 +15048,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15080,17 +15092,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -15458,7 +15470,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15838,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -16632,7 +16644,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16676,17 +16688,17 @@
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17140,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17172,17 +17184,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -17306,7 +17318,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17442,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17554,7 +17566,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -17748,7 +17760,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17802,7 +17814,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -17872,7 +17884,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -18120,7 +18132,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18244,7 +18256,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18288,17 +18300,17 @@
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -18546,7 +18558,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -18670,7 +18682,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19682,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -20236,7 +20248,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20280,17 +20292,17 @@
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -20414,7 +20426,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -20538,7 +20550,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -21410,7 +21422,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -21716,7 +21728,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -22142,7 +22154,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22212,7 +22224,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22256,17 +22268,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -22460,7 +22472,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22504,17 +22516,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -22762,7 +22774,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -22886,7 +22898,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -22956,7 +22968,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23010,7 +23022,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -23820,7 +23832,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -24242,7 +24254,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -24490,7 +24502,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -24680,7 +24692,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24767,32 +24779,36 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -24800,7 +24816,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24824,17 +24840,17 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr">
@@ -24844,17 +24860,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -24887,32 +24903,36 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -24920,7 +24940,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24944,17 +24964,17 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA198" s="2" t="inlineStr">
@@ -24964,17 +24984,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -25007,32 +25027,36 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N199" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -25040,7 +25064,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25064,17 +25088,17 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA199" s="2" t="inlineStr">
@@ -25084,17 +25108,17 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -25160,7 +25184,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25214,7 +25238,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -25280,7 +25304,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25776,7 +25800,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25820,17 +25844,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -26070,7 +26094,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26384,7 +26408,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26428,12 +26452,12 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
@@ -26562,7 +26586,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -27058,7 +27082,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -27306,7 +27330,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27500,7 +27524,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -28038,7 +28062,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28220,7 +28244,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28264,17 +28288,17 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28642,7 +28666,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28712,7 +28736,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28756,12 +28780,12 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
@@ -29328,7 +29352,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29754,7 +29778,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30266,7 +30290,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31134,7 +31158,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32250,7 +32274,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32936,7 +32960,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32980,17 +33004,17 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33114,7 +33138,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -33304,7 +33328,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33348,12 +33372,12 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
@@ -33478,7 +33502,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33796,7 +33820,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -34098,7 +34122,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -34346,7 +34370,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35090,7 +35114,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -35160,7 +35184,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35204,17 +35228,17 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -35404,7 +35428,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35448,12 +35472,12 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
@@ -35582,7 +35606,7 @@
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35900,7 +35924,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -36322,7 +36346,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -36570,7 +36594,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36938,7 +36962,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -37186,7 +37210,7 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37256,7 +37280,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37300,17 +37324,17 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -37504,7 +37528,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37548,12 +37572,12 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
@@ -37682,7 +37706,7 @@
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -37752,7 +37776,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37963,32 +37987,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -37996,7 +38024,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38020,17 +38048,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -38040,17 +38068,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -38083,32 +38111,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -38116,7 +38148,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38140,17 +38172,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38160,12 +38192,12 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
@@ -38236,7 +38268,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
